--- a/Attendence list.xlsx
+++ b/Attendence list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trash\#863 XC Export\xc_export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Wind3style\workspace\xc_export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A444D00A-239B-4104-A9B1-177E72723801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4E5D61-AF0E-4E9C-8718-B599A59C6722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C5209F01-11F8-4536-83CC-330C0F186448}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C5209F01-11F8-4536-83CC-330C0F186448}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>mshpadi</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Number</t>
   </si>
@@ -69,39 +66,18 @@
     <t>Alexandra.G</t>
   </si>
   <si>
-    <t>Svetlana Svetlichnaya</t>
-  </si>
-  <si>
-    <t>Svetlana</t>
-  </si>
-  <si>
-    <t>Maksim Shpadi</t>
-  </si>
-  <si>
     <t>LauraVinchuk</t>
   </si>
   <si>
     <t>Laura Vinchuk</t>
   </si>
   <si>
-    <t>Alexei Tarasov</t>
-  </si>
-  <si>
-    <t>theoretic</t>
-  </si>
-  <si>
     <t>makovskiyss74</t>
   </si>
   <si>
     <t>Sergey Makovskiy</t>
   </si>
   <si>
-    <t>TeleNata</t>
-  </si>
-  <si>
-    <t>Telemissova Natalia</t>
-  </si>
-  <si>
     <t>Alexey Tulovskiy</t>
   </si>
   <si>
@@ -117,13 +93,19 @@
     <t>Natalya</t>
   </si>
   <si>
-    <t>Bedin Yuriy</t>
-  </si>
-  <si>
-    <t>yurchik_</t>
-  </si>
-  <si>
     <t>Наташа Изотова</t>
+  </si>
+  <si>
+    <t>Sergey Demchenko</t>
+  </si>
+  <si>
+    <t>Demcenko</t>
+  </si>
+  <si>
+    <t>Proudbird</t>
+  </si>
+  <si>
+    <t>Veronika Blagoveshchenskaya</t>
   </si>
 </sst>
 </file>
@@ -167,12 +149,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -188,9 +171,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +211,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -334,7 +317,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,191 +467,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BB7798-2C08-49E6-835C-257ED4D1D79F}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>124</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>1001</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>117</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="B5">
-        <v>1002</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <v>1003</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>1004</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11">
-        <v>1006</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>1007</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
-        <v>1008</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14">
-        <v>1009</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15">
-        <v>1010</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16">
-        <v>1011</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Attendence list.xlsx
+++ b/Attendence list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Wind3style\workspace\xc_export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4E5D61-AF0E-4E9C-8718-B599A59C6722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F179662-F2AC-469B-A8E7-3F2B29762E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C5209F01-11F8-4536-83CC-330C0F186448}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Number</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Veronika Blagoveshchenskaya</t>
+  </si>
+  <si>
+    <t>tg_username</t>
   </si>
 </sst>
 </file>
@@ -467,153 +470,159 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51BB7798-2C08-49E6-835C-257ED4D1D79F}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="1" max="2" width="16.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>22</v>
       </c>
     </row>
